--- a/ig/ch-elm/ValueSet-ch-elm-results-component-antibiotic-cpe.xlsx
+++ b/ig/ch-elm/ValueSet-ch-elm-results-component-antibiotic-cpe.xlsx
@@ -29,7 +29,7 @@
     <t>Version</t>
   </si>
   <si>
-    <t>1.13.1</t>
+    <t>1.14.0</t>
   </si>
   <si>
     <t>Name</t>
@@ -59,7 +59,7 @@
     <t>Date</t>
   </si>
   <si>
-    <t>2026-01-21T11:21:00+00:00</t>
+    <t>2026-05-26T14:58:40+00:00</t>
   </si>
   <si>
     <t>Publisher</t>

--- a/ig/ch-elm/ValueSet-ch-elm-results-component-antibiotic-cpe.xlsx
+++ b/ig/ch-elm/ValueSet-ch-elm-results-component-antibiotic-cpe.xlsx
@@ -29,7 +29,7 @@
     <t>Version</t>
   </si>
   <si>
-    <t>1.14.0</t>
+    <t>1.14.1</t>
   </si>
   <si>
     <t>Name</t>
@@ -59,7 +59,7 @@
     <t>Date</t>
   </si>
   <si>
-    <t>2026-05-26T14:58:40+00:00</t>
+    <t>2026-07-01T19:23:08+00:00</t>
   </si>
   <si>
     <t>Publisher</t>
